--- a/tests/xyz/Example_Cylindrical_Pore/Example_Output_Files/PSD_Plot.xlsx
+++ b/tests/xyz/Example_Cylindrical_Pore/Example_Output_Files/PSD_Plot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PrO-VAT/tests/xyz/Example_Cylindrical_Pore/Example_Output_Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PARSE/tests/xyz/Example_Cylindrical_Pore/Example_Output_Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC55190A-8EF3-4A72-8B9C-C653467D96D4}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299F216B-9542-4B0C-AEC8-2197B12BCCAB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
@@ -3005,10 +3005,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
